--- a/MVAR_ATSBS_T2W/mvar_p50_atsbs_t2w_BICYCLE_WALK.xlsx
+++ b/MVAR_ATSBS_T2W/mvar_p50_atsbs_t2w_BICYCLE_WALK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/MVAR_ATSBS_T2W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030351A4-1B9E-BD4F-AC3A-CDD4CF14DC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC62DB0-A7BC-714A-9E10-7DA86C304287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="14320" xr2:uid="{8F259DD8-93C5-2C49-A1A9-8FF4AA32EA25}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="14280" xr2:uid="{8F259DD8-93C5-2C49-A1A9-8FF4AA32EA25}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="31">
   <si>
     <t>district_name</t>
   </si>
@@ -220,13 +220,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -570,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A91ECAB-36EF-B646-BEC0-678022009BB0}">
-  <dimension ref="A1:AM25"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.1640625" customWidth="1"/>
@@ -579,7 +586,7 @@
     <col min="8" max="8" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -592,11 +599,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="7"/>
+      <c r="I1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="T1" s="1" t="s">
@@ -626,8 +633,11 @@
       <c r="AM1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:39" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AO1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -640,13 +650,12 @@
       <c r="D2" s="3">
         <v>4.1795689999999999</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2" s="6"/>
       <c r="T2" s="1">
         <v>3</v>
       </c>
@@ -672,7 +681,7 @@
         <v>4.1795689999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -685,13 +694,13 @@
       <c r="D3" s="3">
         <v>2.7827199999999999</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>-7.3779482681357728E-2</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>1</v>
       </c>
       <c r="T3" s="1">
@@ -706,10 +715,10 @@
       <c r="W3" s="3">
         <v>3.6038389999999998</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="Y3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Z3" s="9"/>
+      <c r="Z3" s="8"/>
       <c r="AJ3" s="1">
         <v>2</v>
       </c>
@@ -722,8 +731,12 @@
       <c r="AM3" s="3">
         <v>2.7827199999999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AO3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP3" s="12"/>
+    </row>
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -748,10 +761,10 @@
       <c r="W4" s="3">
         <v>2.7476090000000002</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" t="s">
         <v>7</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4">
         <v>0.44385913878764949</v>
       </c>
       <c r="AJ4" s="1">
@@ -766,8 +779,14 @@
       <c r="AM4" s="3">
         <v>2.2407919999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AO4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP4" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -792,14 +811,20 @@
       <c r="W5" s="3">
         <v>2.8338070000000002</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" t="s">
         <v>8</v>
       </c>
-      <c r="Z5" s="6">
+      <c r="Z5">
         <v>0.19701093508531387</v>
       </c>
-    </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AO5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP5" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>7</v>
       </c>
@@ -824,14 +849,20 @@
       <c r="W6" s="3">
         <v>2.4946600000000001</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Y6" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="Z6">
         <v>-0.33831510819114358</v>
       </c>
-    </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AO6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP6" s="9">
+        <v>65535</v>
+      </c>
+    </row>
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>8</v>
       </c>
@@ -859,14 +890,20 @@
       <c r="W7" s="3">
         <v>2.3836249999999999</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Y7" t="s">
         <v>10</v>
       </c>
-      <c r="Z7" s="6">
+      <c r="Z7">
         <v>1.1258469805766466E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:39" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AO7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>10</v>
       </c>
@@ -879,14 +916,20 @@
       <c r="D8" s="3">
         <v>2.2407919999999999</v>
       </c>
-      <c r="Y8" s="7" t="s">
+      <c r="Y8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="Z8" s="7">
+      <c r="Z8" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AO8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP8" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>11</v>
       </c>
@@ -899,12 +942,12 @@
       <c r="D9" s="3">
         <v>2.8338070000000002</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="1:39" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>12</v>
       </c>
@@ -917,400 +960,565 @@
       <c r="D10" s="3">
         <v>2.4946600000000001</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10">
         <v>0.63030374998998873</v>
       </c>
       <c r="Y10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="H11" s="6" t="s">
+      <c r="AO10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11">
         <v>0.39728281725144216</v>
       </c>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8" t="s">
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AA11" s="8" t="s">
+      <c r="AA11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AB11" s="8" t="s">
+      <c r="AB11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="AC11" s="8" t="s">
+      <c r="AC11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AD11" s="8" t="s">
+      <c r="AD11" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="H12" s="6" t="s">
+      <c r="AO11" s="11"/>
+      <c r="AP11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AR11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AS11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="AT11" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12">
         <v>0.19637708966858955</v>
       </c>
-      <c r="Y12" s="6" t="s">
+      <c r="Y12" t="s">
         <v>13</v>
       </c>
-      <c r="Z12" s="6">
+      <c r="Z12">
         <v>2</v>
       </c>
-      <c r="AA12" s="6">
+      <c r="AA12">
         <v>9.3295498757935255E-5</v>
       </c>
-      <c r="AB12" s="6">
+      <c r="AB12">
         <v>4.6647749378967628E-5</v>
       </c>
-      <c r="AC12" s="6">
+      <c r="AC12">
         <v>0.36802045699011865</v>
       </c>
       <c r="AD12" s="5">
         <v>0.71955574778037801</v>
       </c>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="H13" s="6" t="s">
+      <c r="AO12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP12" s="9">
+        <v>2</v>
+      </c>
+      <c r="AQ12" s="9">
+        <v>2.9655987066466681E-3</v>
+      </c>
+      <c r="AR12" s="9">
+        <v>1.4827993533233341E-3</v>
+      </c>
+      <c r="AS12" s="9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AT12" s="9" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13">
         <v>2.1118375515440171E-2</v>
       </c>
-      <c r="Y13" s="6" t="s">
+      <c r="Y13" t="s">
         <v>14</v>
       </c>
-      <c r="Z13" s="6">
+      <c r="Z13">
         <v>3</v>
       </c>
-      <c r="AA13" s="6">
+      <c r="AA13">
         <v>3.8025942710206561E-4</v>
       </c>
-      <c r="AB13" s="6">
+      <c r="AB13">
         <v>1.2675314236735519E-4</v>
       </c>
-      <c r="AC13" s="6"/>
-      <c r="AD13" s="6"/>
-    </row>
-    <row r="14" spans="1:39" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H14" s="7" t="s">
+      <c r="AO13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="9">
+        <v>65535</v>
+      </c>
+      <c r="AS13" s="9"/>
+      <c r="AT13" s="9"/>
+    </row>
+    <row r="14" spans="1:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="6">
         <v>9</v>
       </c>
-      <c r="Y14" s="7" t="s">
+      <c r="Y14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Z14" s="7">
+      <c r="Z14" s="6">
         <v>5</v>
       </c>
-      <c r="AA14" s="7">
+      <c r="AA14" s="6">
         <v>4.7355492586000086E-4</v>
       </c>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
-    </row>
-    <row r="15" spans="1:39" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:39" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AO14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP14" s="10">
+        <v>2</v>
+      </c>
+      <c r="AQ14" s="10">
+        <v>2.9655987066466681E-3</v>
+      </c>
+      <c r="AR14" s="10"/>
+      <c r="AS14" s="10"/>
+      <c r="AT14" s="10"/>
+    </row>
+    <row r="15" spans="1:49" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="H16" t="s">
         <v>12</v>
       </c>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8" t="s">
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="AA16" s="8" t="s">
+      <c r="AA16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="AB16" s="8" t="s">
+      <c r="AB16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="AC16" s="8" t="s">
+      <c r="AC16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AD16" s="8" t="s">
+      <c r="AD16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AE16" s="8" t="s">
+      <c r="AE16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AF16" s="8" t="s">
+      <c r="AF16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AG16" s="8" t="s">
+      <c r="AG16" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="8:33" x14ac:dyDescent="0.2">
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
+      <c r="AO16" s="11"/>
+      <c r="AP16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AQ16" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT16" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU16" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="AV16" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW16" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="8:49" x14ac:dyDescent="0.2">
+      <c r="H17" s="7"/>
+      <c r="I17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="L17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M17" s="8" t="s">
+      <c r="M17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="Y17" s="6" t="s">
+      <c r="Y17" t="s">
         <v>16</v>
       </c>
-      <c r="Z17" s="6">
+      <c r="Z17">
         <v>-0.13431788718709856</v>
       </c>
-      <c r="AA17" s="6">
+      <c r="AA17">
         <v>3.1433099170829433E-2</v>
       </c>
-      <c r="AB17" s="6">
+      <c r="AB17">
         <v>-4.2731353487329162</v>
       </c>
-      <c r="AC17" s="6">
+      <c r="AC17">
         <v>2.3529295925554635E-2</v>
       </c>
-      <c r="AD17" s="6">
+      <c r="AD17">
         <v>-0.2343520375069211</v>
       </c>
-      <c r="AE17" s="6">
+      <c r="AE17">
         <v>-3.428373686727601E-2</v>
       </c>
-      <c r="AF17" s="6">
+      <c r="AF17">
         <v>-0.2343520375069211</v>
       </c>
-      <c r="AG17" s="6">
+      <c r="AG17">
         <v>-3.428373686727601E-2</v>
       </c>
-    </row>
-    <row r="18" spans="8:33" x14ac:dyDescent="0.2">
-      <c r="H18" s="6" t="s">
+      <c r="AO17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP17" s="9">
+        <v>-0.10101930825346868</v>
+      </c>
+      <c r="AQ17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="9">
+        <v>65535</v>
+      </c>
+      <c r="AS17" s="9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AT17" s="9" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AU17" s="9" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AV17" s="9">
+        <v>-0.10101930825346868</v>
+      </c>
+      <c r="AW17" s="9">
+        <v>-0.10101930825346868</v>
+      </c>
+    </row>
+    <row r="18" spans="8:49" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
         <v>13</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18">
         <v>2</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18">
         <v>1.7638371092420341E-3</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18">
         <v>8.8191855462101706E-4</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18">
         <v>1.9774588909497592</v>
       </c>
       <c r="M18" s="5">
         <v>0.21894786697738602</v>
       </c>
-      <c r="Y18" s="6" t="s">
+      <c r="Y18" t="s">
         <v>1</v>
       </c>
-      <c r="Z18" s="6">
+      <c r="Z18">
         <v>1.8590887732895185E-4</v>
       </c>
-      <c r="AA18" s="6">
+      <c r="AA18">
         <v>3.3122376885156668E-4</v>
       </c>
-      <c r="AB18" s="6">
+      <c r="AB18">
         <v>0.56127879340768061</v>
       </c>
-      <c r="AC18" s="6">
+      <c r="AC18">
         <v>0.61380390042761102</v>
       </c>
-      <c r="AD18" s="6">
+      <c r="AD18">
         <v>-8.6819298207486181E-4</v>
       </c>
-      <c r="AE18" s="6">
+      <c r="AE18">
         <v>1.2400107367327654E-3</v>
       </c>
-      <c r="AF18" s="6">
+      <c r="AF18">
         <v>-8.6819298207486181E-4</v>
       </c>
-      <c r="AG18" s="6">
+      <c r="AG18">
         <v>1.2400107367327654E-3</v>
       </c>
-    </row>
-    <row r="19" spans="8:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H19" s="6" t="s">
+      <c r="AO18" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP18" s="9">
+        <v>-3.9930643261888365E-3</v>
+      </c>
+      <c r="AQ18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="9">
+        <v>65535</v>
+      </c>
+      <c r="AS18" s="9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AT18" s="9">
+        <v>-3.9930643261888365E-3</v>
+      </c>
+      <c r="AU18" s="9">
+        <v>-3.9930643261888365E-3</v>
+      </c>
+      <c r="AV18" s="9">
+        <v>-3.9930643261888365E-3</v>
+      </c>
+      <c r="AW18" s="9">
+        <v>-3.9930643261888365E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="8:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19">
         <v>6</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19">
         <v>2.6759147064668574E-3</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19">
         <v>4.459857844111429E-4</v>
       </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="Y19" s="7" t="s">
+      <c r="Y19" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="Z19" s="7">
+      <c r="Z19" s="6">
         <v>-4.2211970520451758E-3</v>
       </c>
-      <c r="AA19" s="7">
+      <c r="AA19" s="6">
         <v>9.5606715793230251E-3</v>
       </c>
-      <c r="AB19" s="7">
+      <c r="AB19" s="6">
         <v>-0.44151679272975003</v>
       </c>
-      <c r="AC19" s="7">
+      <c r="AC19" s="6">
         <v>0.6887241265833709</v>
       </c>
-      <c r="AD19" s="7">
+      <c r="AD19" s="6">
         <v>-3.4647520995692703E-2</v>
       </c>
-      <c r="AE19" s="7">
+      <c r="AE19" s="6">
         <v>2.620512689160235E-2</v>
       </c>
-      <c r="AF19" s="7">
+      <c r="AF19" s="6">
         <v>-3.4647520995692703E-2</v>
       </c>
-      <c r="AG19" s="7">
+      <c r="AG19" s="6">
         <v>2.620512689160235E-2</v>
       </c>
-    </row>
-    <row r="20" spans="8:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H20" s="7" t="s">
+      <c r="AO19" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP19" s="10">
+        <v>-1.0667640553077999E-2</v>
+      </c>
+      <c r="AQ19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="10">
+        <v>65535</v>
+      </c>
+      <c r="AS19" s="10" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AT19" s="10">
+        <v>-1.0667640553077999E-2</v>
+      </c>
+      <c r="AU19" s="10">
+        <v>-1.0667640553077999E-2</v>
+      </c>
+      <c r="AV19" s="10">
+        <v>-1.0667640553077999E-2</v>
+      </c>
+      <c r="AW19" s="10">
+        <v>-1.0667640553077999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="8:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="6">
         <v>8</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="6">
         <v>4.4397518157088915E-3</v>
       </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-    </row>
-    <row r="21" spans="8:33" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="8:33" x14ac:dyDescent="0.2">
-      <c r="H22" s="8"/>
-      <c r="I22" s="8" t="s">
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+    </row>
+    <row r="21" spans="8:49" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="8:49" x14ac:dyDescent="0.2">
+      <c r="H22" s="7"/>
+      <c r="I22" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="K22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="L22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="M22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N22" s="8" t="s">
+      <c r="N22" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="O22" s="8" t="s">
+      <c r="O22" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P22" s="8" t="s">
+      <c r="P22" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="8:33" x14ac:dyDescent="0.2">
-      <c r="H23" s="6" t="s">
+    <row r="23" spans="8:49" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
         <v>16</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23">
         <v>-8.6249846178297868E-2</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23">
         <v>3.5913116875043082E-2</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23">
         <v>-2.4016251911076822</v>
       </c>
       <c r="L23" s="5">
         <v>5.3177000140686013E-2</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23">
         <v>-0.17412607747139519</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23">
         <v>1.6263851147994477E-3</v>
       </c>
-      <c r="O23" s="6">
+      <c r="O23">
         <v>-0.17412607747139519</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P23">
         <v>1.6263851147994477E-3</v>
       </c>
     </row>
-    <row r="24" spans="8:33" x14ac:dyDescent="0.2">
-      <c r="H24" s="6" t="s">
+    <row r="24" spans="8:49" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24">
         <v>1.0026653375402543E-4</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24">
         <v>5.1044167149559669E-4</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24">
         <v>0.19643093296094727</v>
       </c>
       <c r="L24" s="5">
         <v>0.85075728526805228</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24">
         <v>-1.1487392415467975E-3</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24">
         <v>1.3492723090548484E-3</v>
       </c>
-      <c r="O24" s="6">
+      <c r="O24">
         <v>-1.1487392415467975E-3</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24">
         <v>1.3492723090548484E-3</v>
       </c>
     </row>
-    <row r="25" spans="8:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H25" s="7" t="s">
+    <row r="25" spans="8:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H25" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="6">
         <v>-2.1981312698121331E-2</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J25" s="6">
         <v>1.1220184717672187E-2</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="6">
         <v>-1.9590865258661907</v>
       </c>
       <c r="L25" s="4">
         <v>9.7818946121178585E-2</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="6">
         <v>-4.9436115655829081E-2</v>
       </c>
-      <c r="N25" s="7">
+      <c r="N25" s="6">
         <v>5.4734902595864185E-3</v>
       </c>
-      <c r="O25" s="7">
+      <c r="O25" s="6">
         <v>-4.9436115655829081E-2</v>
       </c>
-      <c r="P25" s="7">
+      <c r="P25" s="6">
         <v>5.4734902595864185E-3</v>
       </c>
     </row>
